--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136548881</v>
       </c>
       <c r="B14" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136548881</v>
       </c>
       <c r="B14" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136548881</v>
       </c>
       <c r="B14" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136548881</v>
       </c>
       <c r="B14" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136548881</v>
+        <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>108378</v>
+        <v>99355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220083</v>
+        <v>219811</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Z692 Hotagen, Jmt</t>
+          <t>Solvika, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458477</v>
+        <v>458569</v>
       </c>
       <c r="R14" t="n">
-        <v>7109598</v>
+        <v>7109444</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,20 +2037,126 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933430</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136548881</v>
+      </c>
+      <c r="B15" t="n">
+        <v>108378</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Z692 Hotagen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458477</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7109598</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Väg och Miljö AB</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136548881</t>
         </is>
@@ -2071,6 +2177,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537306</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136538146</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538178</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136538241</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136538301</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136538389</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538410</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538433</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136538434</v>
       </c>
       <c r="B10" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136541084</v>
       </c>
       <c r="B11" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136548757</v>
       </c>
       <c r="B12" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136548869</v>
       </c>
       <c r="B13" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548881</v>
       </c>
       <c r="B15" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 59369-2025 artfynd.xlsx
+++ b/artfynd/A 59369-2025 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>136933430</v>
       </c>
       <c r="B14" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
